--- a/research/ANZ.NZ/Reports/ANZ.NZ_DCF_Model.xlsx
+++ b/research/ANZ.NZ/Reports/ANZ.NZ_DCF_Model.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="117">
   <si>
     <t>ANZ.NZ - ANZ Group Holdings - Bank Earnings DCF (Base Case)</t>
   </si>
@@ -233,10 +233,7 @@
     <t>CoE \ Term G</t>
   </si>
   <si>
-    <t>Note: several upper-left cells are flat because the 12x exit-P/E cap binds before Gordon growth would otherwise -- the terminal-value cap working as intended.</t>
-  </si>
-  <si>
-    <t>Note: several upper-left cells are flat because the 12x exit-P/E cap binds before Gordon growth would otherwise (at low CoE / high growth the Gordon perpetuity would exceed 12x mature earnings, so the cap holds intrinsic value down) -- this is the terminal-value cap working as intended, not a calculation error.</t>
+    <t>Base-case NPAT/growth/payout/exit-multiple structure held constant; cost of equity and terminal growth varied. Several upper-left cells are flat because the 12x exit-P/E cap binds before Gordon growth would otherwise, capping intrinsic value even as CoE falls or terminal growth rises -- this is the terminal-value cap working as intended, not a calculation error.</t>
   </si>
   <si>
     <t>Historical P/E and P/B (ANZ.AX, FY-end Sept close vs FY EPS/BVPS)</t>
@@ -305,13 +302,16 @@
     <t>Implied P/B (vs FY2025 BVPS)</t>
   </si>
   <si>
+    <t>Implied Multiples (Current Market Price)</t>
+  </si>
+  <si>
     <t>Sanity Check Passed?</t>
   </si>
   <si>
     <t>YES</t>
   </si>
   <si>
-    <t>The current market price (NZ$45.17, ~A$37.68) implies a much richer P/E of ~19.0x FY2025 EPS and P/B of ~1.61x -- both ABOVE the 10-year historical average (13.3x / 1.26x) and near the top of the 10-year range, reflecting the stock's strong rally over the past 12 months (ANZ.AX roughly $25 to $37.68 AUD-equivalent) on H1-2026 recovery optimism. The DCF's base-case intrinsic value of A$23.52 (implied P/E 11.9x, P/B 1.0x) sits comfortably WITHIN the historical range, i.e. the model is not producing an implausible output -- it is flagging that the market is currently paying a premium to ANZ's own historical multiple range for the post-Matos turnaround thesis to play out. No sanity-check fix was required.</t>
+    <t>The current market price (NZ$45.17, ~A$37.68) implies a much richer P/E of ~19.0x FY2025 EPS and P/B of ~1.61x -- both ABOVE the 10-year historical average (13.3x / 1.26x) and near or above the top of the 10-year range, reflecting the stock's strong rally over the past 12 months (ANZ.AX roughly $25 to $37.7 AUD-equivalent) on H1-2026 recovery optimism (cash profit +6% YoY, cash ROTE +161bps to 11.6%, cost-to-income cash improved to 49.4%) and the completed Worldline buyout. The DCF's base-case intrinsic value of A$23.52 (implied P/E 11.9x, P/B 1.0x) sits comfortably WITHIN the historical range, i.e. the model is not producing an implausible output -- it is flagging that the market is currently paying a premium to ANZ's own historical multiple range for the post-Matos turnaround thesis (Suncorp synergies, ANZ Plus rollout, cost-out) to play out in full, while the APRA CEU / $1bn capital add-on overhang and NZ mortgage-share losses remain unresolved. No sanity-check fix was required.</t>
   </si>
   <si>
     <t>Model Provenance &amp; Notes</t>
@@ -326,37 +326,37 @@
     <t>Build date</t>
   </si>
   <si>
-    <t>2026-08-08</t>
+    <t>2026-08-09</t>
   </si>
   <si>
     <t>Data vintage</t>
   </si>
   <si>
-    <t>Share price: NZX ANZ.NZ close fetched live 2026-08-08 (NZ$45.17). Financials: FY2025 10-K/Annual Report (year ended 30 Sep 2025) and H1-2026 interim report (to 31 Mar 2026). Historical multiples use ANZ.AX (ASX line) 10-year monthly closes fetched live from Yahoo Finance on 2026-08-08.</t>
+    <t>Share price: NZX ANZ.NZ close fetched live 2026-08-09 (NZ$45.17). Financials: FY2025 Annual Report (year ended 30 Sep 2025) and H1-2026 interim report (to 31 Mar 2026). Historical multiples use ANZ.AX (ASX line) 10-year monthly closes re-fetched live from Yahoo Finance on 2026-08-09.</t>
   </si>
   <si>
     <t>FX rate used</t>
   </si>
   <si>
-    <t>AUD/NZD = 1.1988 (fetched/quoted 2026-08-08). Model built in AUD; NZD figures = AUD figure x this rate.</t>
+    <t>AUD/NZD = 1.1988 (re-verified live 2026-08-09, unchanged from prior run). Model built in AUD; NZD figures = AUD figure x this rate.</t>
   </si>
   <si>
     <t>Model type</t>
   </si>
   <si>
-    <t>Earnings-at-cost-of-equity (bank/financial model), NOT an owner-FCF DCF. See valuation_philosophy block in the JSON for full rationale.</t>
+    <t>Earnings-at-cost-of-equity (bank/financial), NOT owner-FCF DCF. See valuation_philosophy block in the JSON for full rationale.</t>
   </si>
   <si>
     <t>Key methodology choices</t>
   </si>
   <si>
-    <t>1) Base-case starting NPAT is a mid-cycle normalization (A$6.5bn), not the FY2025 actual (A$6.035bn, depressed by ~A$250m ASIC penalties/restructuring) nor the H1-2026 annualized run-rate (A$7.3bn, single-half momentum). 2) Terminal value = lower of Gordon growth perpetuity and an exit-P/E cap (12x base, anchored to the 10yr average historical P/E of 13.3x with a modest discount for ongoing APRA remediation). 3) Discounting uses cost of equity (10.5% base), not WACC -- appropriate for a bank where debt/deposits are funding, not capital structure leverage subject to a blended discount rate. 4) No net-debt adjustment anywhere -- deposits and wholesale debt fund the loan book and are not netted against value. 5) Entry price discounts 5 years of base-case dividends per share plus a year-5 exit value (Y5 EPS x exit-P/E) at a 15% hurdle, per share.</t>
+    <t>1) Base-case starting NPAT is a mid-cycle normalization (A$6.5bn), not the FY2025 actual (A$6.035bn, depressed by ~A$250m ASIC penalties/restructuring) nor the H1-2026 annualized run-rate (A$7.3bn, single-half momentum). 2) Terminal value = lower of Gordon growth perpetuity (applied to year-5 EPS as the earnings-power base) and an exit-P/E cap (12x base, anchored to the 10yr average historical P/E of 13.27x with a modest discount for ongoing APRA remediation). 3) Discounting uses cost of equity (10.5% base), not WACC -- appropriate for a bank where debt/deposits are funding, not capital structure leverage subject to a blended discount rate. 4) No net-debt adjustment anywhere -- deposits and wholesale debt fund the loan book and are not netted against value. 5) Entry price discounts 5 years of base-case dividends per share plus a year-5 exit value (Y5 EPS x exit-P/E) at a 15% hurdle, per share.</t>
   </si>
   <si>
     <t>What to refresh after next earnings</t>
   </si>
   <si>
-    <t>FY2026 annual report (due ~Nov 2026): update NPAT/EPS/DPS actuals, re-check whether FY2025 one-offs (ASIC penalties, restructuring) have fully cleared, re-verify payout ratio and buyback status (paused as at H1-2026), and refresh the live share price and AUD/NZD FX rate.</t>
+    <t>FY2026 annual report (due ~Nov 2026): update NPAT/EPS/DPS actuals, re-check whether FY2025 one-offs (ASIC penalties, restructuring) have fully cleared, monitor whether the APRA $1bn operational-risk capital add-on is reduced, re-verify payout ratio and buyback status (ceased as at H1-2026), track Suncorp migration progress (34% complete at March 2026, targeting full migration by June 2027), and refresh the live share price and AUD/NZD FX rate.</t>
   </si>
   <si>
     <t>Cell colour conventions</t>
@@ -376,10 +376,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="164" formatCode="#,##0.00"/>
-    <numFmt numFmtId="165" formatCode="0.0%"/>
-    <numFmt numFmtId="166" formatCode="#,##0.0"/>
-    <numFmt numFmtId="167" formatCode="&quot;A$&quot;#,##0.00"/>
+    <numFmt numFmtId="164" formatCode="#,##0.0000"/>
+    <numFmt numFmtId="165" formatCode="&quot;A$&quot;#,##0.00"/>
+    <numFmt numFmtId="166" formatCode="0.0%"/>
+    <numFmt numFmtId="167" formatCode="#,##0.00"/>
     <numFmt numFmtId="168" formatCode="&quot;NZ$&quot;#,##0.00"/>
   </numFmts>
   <fonts count="6">
@@ -505,17 +505,17 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="165" fontId="4" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="4" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="167" fontId="4" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="4" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="168" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="166" fontId="4" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -816,8 +816,8 @@
   <dimension ref="A1:F53"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="30.7109375" customWidth="1"/>
-    <col min="2" max="8" width="13.7109375" customWidth="1"/>
+    <col min="1" max="1" width="38.7109375" customWidth="1"/>
+    <col min="2" max="6" width="13.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
@@ -914,7 +914,6 @@
       </c>
     </row>
     <row r="16" spans="1:6">
-      <c r="A16" s="7"/>
       <c r="B16" s="7" t="s">
         <v>13</v>
       </c>
@@ -977,7 +976,6 @@
       </c>
     </row>
     <row r="21" spans="1:6">
-      <c r="A21" s="7"/>
       <c r="B21" s="7" t="s">
         <v>13</v>
       </c>
@@ -1048,23 +1046,23 @@
       <c r="A24" t="s">
         <v>22</v>
       </c>
-      <c r="B24" s="5">
+      <c r="B24" s="9">
         <f>B22/B23</f>
         <v>0</v>
       </c>
-      <c r="C24" s="5">
+      <c r="C24" s="9">
         <f>C22/C23</f>
         <v>0</v>
       </c>
-      <c r="D24" s="5">
+      <c r="D24" s="9">
         <f>D22/D23</f>
         <v>0</v>
       </c>
-      <c r="E24" s="5">
+      <c r="E24" s="9">
         <f>E22/E23</f>
         <v>0</v>
       </c>
-      <c r="F24" s="5">
+      <c r="F24" s="9">
         <f>F22/F23</f>
         <v>0</v>
       </c>
@@ -1073,23 +1071,23 @@
       <c r="A25" t="s">
         <v>23</v>
       </c>
-      <c r="B25" s="5">
+      <c r="B25" s="9">
         <f>B24*$B$12</f>
         <v>0</v>
       </c>
-      <c r="C25" s="5">
+      <c r="C25" s="9">
         <f>C24*$B$12</f>
         <v>0</v>
       </c>
-      <c r="D25" s="5">
+      <c r="D25" s="9">
         <f>D24*$B$12</f>
         <v>0</v>
       </c>
-      <c r="E25" s="5">
+      <c r="E25" s="9">
         <f>E24*$B$12</f>
         <v>0</v>
       </c>
-      <c r="F25" s="5">
+      <c r="F25" s="9">
         <f>F24*$B$12</f>
         <v>0</v>
       </c>
@@ -1098,23 +1096,23 @@
       <c r="A26" t="s">
         <v>24</v>
       </c>
-      <c r="B26" s="5">
+      <c r="B26" s="9">
         <f>1/(1+$B$10)^1</f>
         <v>0</v>
       </c>
-      <c r="C26" s="5">
+      <c r="C26" s="9">
         <f>1/(1+$B$10)^2</f>
         <v>0</v>
       </c>
-      <c r="D26" s="5">
+      <c r="D26" s="9">
         <f>1/(1+$B$10)^3</f>
         <v>0</v>
       </c>
-      <c r="E26" s="5">
+      <c r="E26" s="9">
         <f>1/(1+$B$10)^4</f>
         <v>0</v>
       </c>
-      <c r="F26" s="5">
+      <c r="F26" s="9">
         <f>1/(1+$B$10)^5</f>
         <v>0</v>
       </c>
@@ -1123,23 +1121,23 @@
       <c r="A27" t="s">
         <v>25</v>
       </c>
-      <c r="B27" s="5">
+      <c r="B27" s="9">
         <f>B25*B26</f>
         <v>0</v>
       </c>
-      <c r="C27" s="5">
+      <c r="C27" s="9">
         <f>C25*C26</f>
         <v>0</v>
       </c>
-      <c r="D27" s="5">
+      <c r="D27" s="9">
         <f>D25*D26</f>
         <v>0</v>
       </c>
-      <c r="E27" s="5">
+      <c r="E27" s="9">
         <f>E25*E26</f>
         <v>0</v>
       </c>
-      <c r="F27" s="5">
+      <c r="F27" s="9">
         <f>F25*F26</f>
         <v>0</v>
       </c>
@@ -1162,7 +1160,7 @@
       <c r="A31" t="s">
         <v>28</v>
       </c>
-      <c r="B31" s="5">
+      <c r="B31" s="9">
         <f>F24*(1+B11)</f>
         <v>0</v>
       </c>
@@ -1204,19 +1202,19 @@
       </c>
     </row>
     <row r="36" spans="1:2">
-      <c r="A36" s="9" t="s">
+      <c r="A36" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="B36" s="10">
+      <c r="B36" s="11">
         <f>B30+B35</f>
         <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:2">
-      <c r="A37" s="9" t="s">
+      <c r="A37" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="B37" s="11">
+      <c r="B37" s="12">
         <f>B36*B6</f>
         <v>0</v>
       </c>
@@ -1225,7 +1223,7 @@
       <c r="A39" t="s">
         <v>35</v>
       </c>
-      <c r="B39" s="12">
+      <c r="B39" s="13">
         <f>B35/B36</f>
         <v>0</v>
       </c>
@@ -1234,7 +1232,7 @@
       <c r="A40" t="s">
         <v>36</v>
       </c>
-      <c r="B40" s="5">
+      <c r="B40" s="8">
         <f>B34/F24</f>
         <v>0</v>
       </c>
@@ -1283,7 +1281,7 @@
       <c r="A47" t="s">
         <v>42</v>
       </c>
-      <c r="B47" s="13">
+      <c r="B47" s="5">
         <f>B44+B46</f>
         <v>0</v>
       </c>
@@ -1301,7 +1299,7 @@
       <c r="A49" t="s">
         <v>44</v>
       </c>
-      <c r="B49" s="12">
+      <c r="B49" s="13">
         <f>(B5-B48)/B5</f>
         <v>0</v>
       </c>
@@ -1310,7 +1308,7 @@
       <c r="A50" t="s">
         <v>45</v>
       </c>
-      <c r="B50" s="12">
+      <c r="B50" s="13">
         <f>B48/B37</f>
         <v>0</v>
       </c>
@@ -1324,7 +1322,7 @@
       <c r="A53" t="s">
         <v>47</v>
       </c>
-      <c r="B53" s="12">
+      <c r="B53" s="13">
         <f>(B37-B5)/B5</f>
         <v>0</v>
       </c>
@@ -1339,8 +1337,8 @@
   <dimension ref="A1:D20"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="30.7109375" customWidth="1"/>
-    <col min="2" max="4" width="16.7109375" customWidth="1"/>
+    <col min="1" max="1" width="34.7109375" customWidth="1"/>
+    <col min="2" max="4" width="14.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
@@ -1354,7 +1352,6 @@
       </c>
     </row>
     <row r="4" spans="1:4">
-      <c r="A4" s="7"/>
       <c r="B4" s="7" t="s">
         <v>50</v>
       </c>
@@ -1369,13 +1366,13 @@
       <c r="A5" t="s">
         <v>53</v>
       </c>
-      <c r="B5" s="5">
+      <c r="B5" s="8">
         <v>6500</v>
       </c>
-      <c r="C5" s="5">
+      <c r="C5" s="8">
         <v>6900</v>
       </c>
-      <c r="D5" s="5">
+      <c r="D5" s="8">
         <v>5500</v>
       </c>
     </row>
@@ -1383,13 +1380,13 @@
       <c r="A6" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="12">
+      <c r="B6" s="13">
         <v>0.105</v>
       </c>
-      <c r="C6" s="12">
+      <c r="C6" s="13">
         <v>0.1</v>
       </c>
-      <c r="D6" s="12">
+      <c r="D6" s="13">
         <v>0.12</v>
       </c>
     </row>
@@ -1397,13 +1394,13 @@
       <c r="A7" t="s">
         <v>54</v>
       </c>
-      <c r="B7" s="12">
+      <c r="B7" s="13">
         <v>0.02</v>
       </c>
-      <c r="C7" s="12">
+      <c r="C7" s="13">
         <v>0.025</v>
       </c>
-      <c r="D7" s="12">
+      <c r="D7" s="13">
         <v>0.015</v>
       </c>
     </row>
@@ -1411,13 +1408,13 @@
       <c r="A8" t="s">
         <v>55</v>
       </c>
-      <c r="B8" s="12">
+      <c r="B8" s="13">
         <v>0.7</v>
       </c>
-      <c r="C8" s="12">
+      <c r="C8" s="13">
         <v>0.65</v>
       </c>
-      <c r="D8" s="12">
+      <c r="D8" s="13">
         <v>0.75</v>
       </c>
     </row>
@@ -1425,32 +1422,32 @@
       <c r="A9" t="s">
         <v>56</v>
       </c>
-      <c r="B9" s="5">
+      <c r="B9" s="8">
         <v>12</v>
       </c>
-      <c r="C9" s="5">
+      <c r="C9" s="8">
         <v>13</v>
       </c>
-      <c r="D9" s="5">
+      <c r="D9" s="8">
         <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:4">
-      <c r="A11" s="9" t="s">
+      <c r="A11" t="s">
         <v>57</v>
       </c>
-      <c r="B11" s="13">
+      <c r="B11" s="5">
         <v>23.52</v>
       </c>
-      <c r="C11" s="13">
+      <c r="C11" s="5">
         <v>28.16</v>
       </c>
-      <c r="D11" s="13">
+      <c r="D11" s="5">
         <v>14.99</v>
       </c>
     </row>
     <row r="12" spans="1:4">
-      <c r="A12" s="9" t="s">
+      <c r="A12" t="s">
         <v>58</v>
       </c>
       <c r="B12" s="14">
@@ -1467,13 +1464,13 @@
       <c r="A13" t="s">
         <v>59</v>
       </c>
-      <c r="B13" s="12">
+      <c r="B13" s="13">
         <v>-0.3759</v>
       </c>
-      <c r="C13" s="12">
+      <c r="C13" s="13">
         <v>-0.2527</v>
       </c>
-      <c r="D13" s="12">
+      <c r="D13" s="13">
         <v>-0.6022</v>
       </c>
     </row>
@@ -1481,13 +1478,13 @@
       <c r="A14" t="s">
         <v>60</v>
       </c>
-      <c r="B14" s="12">
+      <c r="B14" s="13">
         <v>0.7440000000000001</v>
       </c>
-      <c r="C14" s="12">
+      <c r="C14" s="13">
         <v>0.778</v>
       </c>
-      <c r="D14" s="12">
+      <c r="D14" s="13">
         <v>0.67</v>
       </c>
     </row>
@@ -1506,7 +1503,7 @@
       </c>
     </row>
     <row r="18" spans="1:2">
-      <c r="A18" s="9" t="s">
+      <c r="A18" s="10" t="s">
         <v>64</v>
       </c>
       <c r="B18" s="14">
@@ -1517,7 +1514,7 @@
       <c r="A19" t="s">
         <v>65</v>
       </c>
-      <c r="B19" s="12">
+      <c r="B19" s="13">
         <v>-0.4017</v>
       </c>
     </row>
@@ -1536,24 +1533,24 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="18.7109375" customWidth="1"/>
-    <col min="2" max="7" width="12.7109375" customWidth="1"/>
+    <col min="1" max="1" width="16.7109375" customWidth="1"/>
+    <col min="2" max="6" width="10.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:6">
       <c r="A2" s="2" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:6">
       <c r="A4" s="7" t="s">
         <v>70</v>
       </c>
@@ -1573,7 +1570,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:6">
       <c r="A5" s="15">
         <v>0.08500000000000001</v>
       </c>
@@ -1593,7 +1590,7 @@
         <v>30.58</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:6">
       <c r="A6" s="15">
         <v>0.095</v>
       </c>
@@ -1613,7 +1610,7 @@
         <v>29.36</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:6">
       <c r="A7" s="15">
         <v>0.105</v>
       </c>
@@ -1633,7 +1630,7 @@
         <v>28.19</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:6">
       <c r="A8" s="15">
         <v>0.115</v>
       </c>
@@ -1653,7 +1650,7 @@
         <v>27.08</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:6">
       <c r="A9" s="15">
         <v>0.125</v>
       </c>
@@ -1673,38 +1670,19 @@
         <v>24.18</v>
       </c>
     </row>
-    <row r="11" spans="1:7">
+    <row r="11" spans="1:6" ht="60" customHeight="1">
       <c r="A11" s="16" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B11" s="16"/>
       <c r="C11" s="16"/>
       <c r="D11" s="16"/>
       <c r="E11" s="16"/>
       <c r="F11" s="16"/>
-      <c r="G11" s="16"/>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12" s="16"/>
-      <c r="B12" s="16"/>
-      <c r="C12" s="16"/>
-      <c r="D12" s="16"/>
-      <c r="E12" s="16"/>
-      <c r="F12" s="16"/>
-      <c r="G12" s="16"/>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13" s="16"/>
-      <c r="B13" s="16"/>
-      <c r="C13" s="16"/>
-      <c r="D13" s="16"/>
-      <c r="E13" s="16"/>
-      <c r="F13" s="16"/>
-      <c r="G13" s="16"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A11:G13"/>
+    <mergeCell ref="A11:F11"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1712,296 +1690,316 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E32"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="10.7109375" customWidth="1"/>
-    <col min="2" max="5" width="14.7109375" customWidth="1"/>
+    <col min="1" max="5" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="B3" s="7" t="s">
         <v>74</v>
-      </c>
-      <c r="B3" s="7" t="s">
-        <v>75</v>
       </c>
       <c r="C3" s="7" t="s">
         <v>22</v>
       </c>
       <c r="D3" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="E3" s="7" t="s">
         <v>76</v>
-      </c>
-      <c r="E3" s="7" t="s">
-        <v>77</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" t="s">
-        <v>78</v>
-      </c>
-      <c r="B4" s="13">
+        <v>77</v>
+      </c>
+      <c r="B4" s="8">
         <v>27.63</v>
       </c>
-      <c r="C4" s="13">
+      <c r="C4" s="9">
         <v>1.974</v>
       </c>
-      <c r="D4" s="5">
+      <c r="D4" s="8">
         <v>14</v>
       </c>
-      <c r="E4" s="5">
+      <c r="E4" s="8">
         <v>1.4</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" t="s">
-        <v>79</v>
-      </c>
-      <c r="B5" s="13">
+        <v>78</v>
+      </c>
+      <c r="B5" s="8">
         <v>29.68</v>
       </c>
-      <c r="C5" s="13">
+      <c r="C5" s="9">
         <v>2.201</v>
       </c>
-      <c r="D5" s="5">
-        <v>13.48</v>
-      </c>
-      <c r="E5" s="5">
+      <c r="D5" s="8">
+        <v>13.49</v>
+      </c>
+      <c r="E5" s="8">
         <v>1.48</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" t="s">
-        <v>80</v>
-      </c>
-      <c r="B6" s="13">
+        <v>79</v>
+      </c>
+      <c r="B6" s="8">
         <v>25.72</v>
       </c>
-      <c r="C6" s="13">
+      <c r="C6" s="9">
         <v>2.216</v>
       </c>
-      <c r="D6" s="5">
+      <c r="D6" s="8">
         <v>11.61</v>
       </c>
-      <c r="E6" s="5">
+      <c r="E6" s="8">
         <v>1.24</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" t="s">
-        <v>81</v>
-      </c>
-      <c r="B7" s="13">
+        <v>80</v>
+      </c>
+      <c r="B7" s="8">
         <v>26.53</v>
       </c>
-      <c r="C7" s="13">
+      <c r="C7" s="9">
         <v>2.1</v>
       </c>
-      <c r="D7" s="5">
+      <c r="D7" s="8">
         <v>12.63</v>
       </c>
-      <c r="E7" s="5">
+      <c r="E7" s="8">
         <v>1.24</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" t="s">
-        <v>82</v>
-      </c>
-      <c r="B8" s="13">
+        <v>81</v>
+      </c>
+      <c r="B8" s="8">
         <v>18.66</v>
       </c>
-      <c r="C8" s="13">
+      <c r="C8" s="9">
         <v>1.264</v>
       </c>
-      <c r="D8" s="5">
+      <c r="D8" s="8">
         <v>14.76</v>
       </c>
-      <c r="E8" s="5">
+      <c r="E8" s="8">
         <v>0.86</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" t="s">
-        <v>83</v>
-      </c>
-      <c r="B9" s="13">
+        <v>82</v>
+      </c>
+      <c r="B9" s="8">
         <v>27.92</v>
       </c>
-      <c r="C9" s="13">
+      <c r="C9" s="9">
         <v>2.153</v>
       </c>
-      <c r="D9" s="5">
+      <c r="D9" s="8">
         <v>12.97</v>
       </c>
-      <c r="E9" s="5">
+      <c r="E9" s="8">
         <v>1.24</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" t="s">
-        <v>84</v>
-      </c>
-      <c r="B10" s="13">
+        <v>83</v>
+      </c>
+      <c r="B10" s="8">
         <v>25.56</v>
       </c>
-      <c r="C10" s="13">
+      <c r="C10" s="9">
         <v>2.5</v>
       </c>
-      <c r="D10" s="5">
+      <c r="D10" s="8">
         <v>10.22</v>
       </c>
-      <c r="E10" s="5">
+      <c r="E10" s="8">
         <v>1.15</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" t="s">
-        <v>85</v>
-      </c>
-      <c r="B11" s="13">
+        <v>84</v>
+      </c>
+      <c r="B11" s="8">
         <v>24.71</v>
       </c>
-      <c r="C11" s="13">
+      <c r="C11" s="9">
         <v>2.391</v>
       </c>
-      <c r="D11" s="5">
+      <c r="D11" s="8">
         <v>10.33</v>
       </c>
-      <c r="E11" s="5">
+      <c r="E11" s="8">
         <v>1.07</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" t="s">
-        <v>86</v>
-      </c>
-      <c r="B12" s="13">
+        <v>85</v>
+      </c>
+      <c r="B12" s="8">
         <v>31.15</v>
       </c>
-      <c r="C12" s="13">
+      <c r="C12" s="9">
         <v>2.196</v>
       </c>
-      <c r="D12" s="5">
+      <c r="D12" s="8">
         <v>14.18</v>
       </c>
-      <c r="E12" s="5">
+      <c r="E12" s="8">
         <v>1.36</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" t="s">
+        <v>86</v>
+      </c>
+      <c r="B13" s="8">
+        <v>36.65</v>
+      </c>
+      <c r="C13" s="9">
+        <v>1.981</v>
+      </c>
+      <c r="D13" s="8">
+        <v>18.5</v>
+      </c>
+      <c r="E13" s="8">
+        <v>1.56</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" t="s">
         <v>87</v>
       </c>
-      <c r="B13" s="13">
-        <v>36.65</v>
-      </c>
-      <c r="C13" s="13">
-        <v>1.981</v>
-      </c>
-      <c r="D13" s="5">
-        <v>18.5</v>
-      </c>
-      <c r="E13" s="5">
-        <v>1.56</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5">
-      <c r="A15" s="9" t="s">
+      <c r="D15" s="8">
+        <v>13.27</v>
+      </c>
+      <c r="E15" s="8">
+        <v>1.26</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16" t="s">
         <v>88</v>
       </c>
-      <c r="D15" s="5">
-        <v>13.27</v>
-      </c>
-      <c r="E15" s="5">
-        <v>1.26</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5">
-      <c r="A16" s="9" t="s">
+      <c r="D16" t="s">
         <v>89</v>
       </c>
-      <c r="D16" t="s">
+      <c r="E16" t="s">
         <v>90</v>
       </c>
-      <c r="E16" t="s">
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="10" t="s">
         <v>91</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="9" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" t="s">
-        <v>93</v>
-      </c>
-      <c r="B20" s="5">
+        <v>92</v>
+      </c>
+      <c r="B20" s="8">
         <v>11.87</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" t="s">
+        <v>93</v>
+      </c>
+      <c r="B21" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="B21" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="9" t="s">
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" t="s">
+        <v>92</v>
+      </c>
+      <c r="B24" s="8">
+        <v>19.02</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" t="s">
+        <v>93</v>
+      </c>
+      <c r="B25" s="8">
+        <v>1.61</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="10" t="s">
         <v>95</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B27" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="16" t="s">
+    <row r="28" spans="1:5" ht="140" customHeight="1">
+      <c r="A28" s="16" t="s">
         <v>97</v>
       </c>
-      <c r="B24" s="16"/>
-      <c r="C24" s="16"/>
-      <c r="D24" s="16"/>
-      <c r="E24" s="16"/>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="16"/>
-      <c r="B25" s="16"/>
-      <c r="C25" s="16"/>
-      <c r="D25" s="16"/>
-      <c r="E25" s="16"/>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="16"/>
-      <c r="B26" s="16"/>
-      <c r="C26" s="16"/>
-      <c r="D26" s="16"/>
-      <c r="E26" s="16"/>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="16"/>
-      <c r="B27" s="16"/>
-      <c r="C27" s="16"/>
-      <c r="D27" s="16"/>
-      <c r="E27" s="16"/>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="16"/>
       <c r="B28" s="16"/>
       <c r="C28" s="16"/>
       <c r="D28" s="16"/>
       <c r="E28" s="16"/>
     </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="16"/>
+      <c r="B29" s="16"/>
+      <c r="C29" s="16"/>
+      <c r="D29" s="16"/>
+      <c r="E29" s="16"/>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="16"/>
+      <c r="B30" s="16"/>
+      <c r="C30" s="16"/>
+      <c r="D30" s="16"/>
+      <c r="E30" s="16"/>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="16"/>
+      <c r="B31" s="16"/>
+      <c r="C31" s="16"/>
+      <c r="D31" s="16"/>
+      <c r="E31" s="16"/>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="16"/>
+      <c r="B32" s="16"/>
+      <c r="C32" s="16"/>
+      <c r="D32" s="16"/>
+      <c r="E32" s="16"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A24:E28"/>
+    <mergeCell ref="A28:E32"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2012,8 +2010,8 @@
   <dimension ref="A1:B12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="28.7109375" customWidth="1"/>
-    <col min="2" max="2" width="90.7109375" customWidth="1"/>
+    <col min="1" max="1" width="24.7109375" customWidth="1"/>
+    <col min="2" max="2" width="100.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -2021,72 +2019,72 @@
         <v>98</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="30" customHeight="1">
-      <c r="A4" s="9" t="s">
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
         <v>99</v>
       </c>
-      <c r="B4" s="16" t="s">
+      <c r="B4" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="30" customHeight="1">
-      <c r="A5" s="9" t="s">
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
         <v>101</v>
       </c>
-      <c r="B5" s="16" t="s">
+      <c r="B5" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="60" customHeight="1">
-      <c r="A6" s="9" t="s">
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
         <v>103</v>
       </c>
       <c r="B6" s="16" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="30" customHeight="1">
-      <c r="A7" s="9" t="s">
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
         <v>105</v>
       </c>
       <c r="B7" s="16" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="30" customHeight="1">
-      <c r="A8" s="9" t="s">
+    <row r="8" spans="1:2">
+      <c r="A8" t="s">
         <v>107</v>
       </c>
       <c r="B8" s="16" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="60" customHeight="1">
-      <c r="A9" s="9" t="s">
+    <row r="9" spans="1:2">
+      <c r="A9" t="s">
         <v>109</v>
       </c>
       <c r="B9" s="16" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="60" customHeight="1">
-      <c r="A10" s="9" t="s">
+    <row r="10" spans="1:2">
+      <c r="A10" t="s">
         <v>111</v>
       </c>
       <c r="B10" s="16" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="11" spans="1:2" ht="60" customHeight="1">
-      <c r="A11" s="9" t="s">
+    <row r="11" spans="1:2">
+      <c r="A11" t="s">
         <v>113</v>
       </c>
       <c r="B11" s="16" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="60" customHeight="1">
-      <c r="A12" s="9" t="s">
+    <row r="12" spans="1:2">
+      <c r="A12" t="s">
         <v>115</v>
       </c>
       <c r="B12" s="16" t="s">
